--- a/out/cable_list_RK071.xlsx
+++ b/out/cable_list_RK071.xlsx
@@ -885,7 +885,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 1X4X0,8 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -912,14 +912,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Storing</t>
+          <t>Brandventilatieschakeling</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -929,14 +929,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Overwerktimer</t>
+          <t>Storing</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 1X4X0,8 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 1X4X0,8 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 1X4X0,8 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -980,14 +980,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Brandmeldcentrale</t>
+          <t>Overwerktimer</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Brandschakelaar toevoer [?]</t>
+          <t>Brandmeldcentrale</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1014,14 +1014,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Brandschakelaar afvoer [?]</t>
+          <t>Brandventilatieschakeling [?]</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
